--- a/Tengine/Configs/GameConfig/Datas/moster.xlsx
+++ b/Tengine/Configs/GameConfig/Datas/moster.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={8E54B6C4-6C45-415A-AE7B-A2B3380E123D}</author>
+    <author>tc={5E0FA19B-CBDA-4150-A5F3-6D94AFC8F731}</author>
   </authors>
   <commentList>
     <comment ref="J1" authorId="0">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t/>
   </si>
@@ -261,6 +261,201 @@
   </si>
   <si>
     <t>intelligence</t>
+  </si>
+  <si>
+    <t>单只资源名</t>
+  </si>
+  <si>
+    <t>群组资源名</t>
+  </si>
+  <si>
+    <t>每组数量</t>
+  </si>
+  <si>
+    <t>resource_name</t>
+  </si>
+  <si>
+    <t>group_resource_name</t>
+  </si>
+  <si>
+    <t>group_count</t>
+  </si>
+  <si>
+    <t>string!</t>
+  </si>
+  <si>
+    <t>int#range=[1,20]</t>
+  </si>
+  <si>
+    <t>紫红史莱姆</t>
+  </si>
+  <si>
+    <t>紫红色的圆团状史莱姆，常聚成小群活动。</t>
+  </si>
+  <si>
+    <t>monster_01_a_1</t>
+  </si>
+  <si>
+    <t>monster_02_a_1</t>
+  </si>
+  <si>
+    <t>浅绿史莱姆</t>
+  </si>
+  <si>
+    <t>浅绿色的软体史莱姆，身体向后拖出柔软的尾状轮廓。</t>
+  </si>
+  <si>
+    <t>monster_01_a_2</t>
+  </si>
+  <si>
+    <t>monster_02_a_2</t>
+  </si>
+  <si>
+    <t>青蓝史莱姆</t>
+  </si>
+  <si>
+    <t>青蓝色的圆团状史莱姆，群聚时互相挤靠。</t>
+  </si>
+  <si>
+    <t>monster_01_b_1</t>
+  </si>
+  <si>
+    <t>monster_02_b_1</t>
+  </si>
+  <si>
+    <t>灰蓝史莱姆</t>
+  </si>
+  <si>
+    <t>灰蓝色的软体史莱姆，聚集成群时仍各自活动。</t>
+  </si>
+  <si>
+    <t>monster_01_b_2</t>
+  </si>
+  <si>
+    <t>monster_02_b_2</t>
+  </si>
+  <si>
+    <t>叶芽史莱姆</t>
+  </si>
+  <si>
+    <t>嫩绿色的史莱姆，头顶长有叶芽。</t>
+  </si>
+  <si>
+    <t>monster_01_c_1</t>
+  </si>
+  <si>
+    <t>monster_02_c_1</t>
+  </si>
+  <si>
+    <t>荆冠史莱姆</t>
+  </si>
+  <si>
+    <t>粉红色的史莱姆，头顶围着一圈荆冠状突起。</t>
+  </si>
+  <si>
+    <t>monster_01_c_2</t>
+  </si>
+  <si>
+    <t>monster_02_c_2</t>
+  </si>
+  <si>
+    <t>暗灰史莱姆</t>
+  </si>
+  <si>
+    <t>暗灰色的圆团状史莱姆，双眼泛红。</t>
+  </si>
+  <si>
+    <t>monster_01_d_1</t>
+  </si>
+  <si>
+    <t>monster_02_d_1</t>
+  </si>
+  <si>
+    <t>黑影史莱姆</t>
+  </si>
+  <si>
+    <t>漆黑的软体史莱姆，眼睛和嘴部呈绿色。</t>
+  </si>
+  <si>
+    <t>monster_01_d_2</t>
+  </si>
+  <si>
+    <t>monster_02_d_2</t>
+  </si>
+  <si>
+    <t>灰鼠</t>
+  </si>
+  <si>
+    <t>灰黑色的鼠怪，背部生有短刺。</t>
+  </si>
+  <si>
+    <t>monster_03_a_1</t>
+  </si>
+  <si>
+    <t>monster_03_a_2</t>
+  </si>
+  <si>
+    <t>沙鼠</t>
+  </si>
+  <si>
+    <t>浅黄色的鼠怪，背部轮廓呈短刺状。</t>
+  </si>
+  <si>
+    <t>monster_03_b_1</t>
+  </si>
+  <si>
+    <t>monster_03_b_2</t>
+  </si>
+  <si>
+    <t>赤焰鼠</t>
+  </si>
+  <si>
+    <t>深红色的鼠怪，身侧带有橙黄色火焰状纹理。</t>
+  </si>
+  <si>
+    <t>monster_03_c_1</t>
+  </si>
+  <si>
+    <t>monster_03_c_2</t>
+  </si>
+  <si>
+    <t>晶背鼠</t>
+  </si>
+  <si>
+    <t>淡紫色的鼠怪，背部带有青蓝色晶体。</t>
+  </si>
+  <si>
+    <t>monster_03_d_1</t>
+  </si>
+  <si>
+    <t>monster_03_d_2</t>
+  </si>
+  <si>
+    <t>赤冠史莱姆</t>
+  </si>
+  <si>
+    <t>暗红色的大体型史莱姆，头顶生有赤红冠状突起。</t>
+  </si>
+  <si>
+    <t>monster_04_a_1</t>
+  </si>
+  <si>
+    <t>双生史莱姆</t>
+  </si>
+  <si>
+    <t>绿色的大体型史莱姆，身体上并列两张面孔。</t>
+  </si>
+  <si>
+    <t>monster_04_b_1</t>
+  </si>
+  <si>
+    <t>巨牙鼠</t>
+  </si>
+  <si>
+    <t>青蓝色的大体型鼠怪，口部生有长牙。</t>
+  </si>
+  <si>
+    <t>monster_04_c_1</t>
   </si>
 </sst>
 </file>
@@ -373,7 +568,7 @@
     <xf numFmtId="300" fontId="11" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="300" fontId="11" fillId="2" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -433,6 +628,13 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -443,7 +645,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="空羽灵" id="{BC0E36AA-D85A-4425-AC3C-B9C6D965493A}"/>
+  <tc2018:person displayName="空羽灵" id="{6C229CA3-6AF3-42F9-A7BA-A6CA3512C066}"/>
 </tc2018:personList>
 </file>
 
@@ -642,7 +844,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="J1" dT="2026-10-08T14:11:22Z" personId="{BC0E36AA-D85A-4425-AC3C-B9C6D965493A}" id="{8E54B6C4-6C45-415A-AE7B-A2B3380E123D}">
+  <threadedComment ref="J1" dT="2026-10-08T14:11:22Z" personId="{6C229CA3-6AF3-42F9-A7BA-A6CA3512C066}" id="{5E0FA19B-CBDA-4150-A5F3-6D94AFC8F731}">
     <text>1=城镇
 2=黑松林
 3=石牙矿洞
@@ -667,51 +869,58 @@
     <col min="9" max="9" width="48" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="19.1914" customWidth="1"/>
+    <col min="13" max="13" width="14.1523" customWidth="1"/>
     <col min="26" max="27" width="20" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39.95" customHeight="1">
+    <row r="1" spans="1:28" ht="39.95" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="J1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>9</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="Z1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="39.95" customHeight="1">
+      <c r="AA1" s="11" t="s"/>
+      <c r="AB1" s="24" t="s"/>
+    </row>
+    <row r="2" spans="1:28" ht="39.95" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
@@ -740,19 +949,24 @@
         <v>65</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>67</v>
       </c>
+      <c r="L2" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>80</v>
+      </c>
       <c r="Z2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="39.95" customHeight="1">
+      <c r="AA2" s="11" t="s"/>
+      <c r="AB2" s="24" t="s"/>
+    </row>
+    <row r="3" spans="1:28" ht="39.95" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>70</v>
       </c>
@@ -781,540 +995,631 @@
         <v>71</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>63</v>
       </c>
+      <c r="L3" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>82</v>
+      </c>
       <c r="Z3" s="20" t="s"/>
       <c r="AA3" s="21" t="s"/>
-    </row>
-    <row r="4" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A4" s="14" t="s"/>
-      <c r="B4" s="7">
+      <c r="AB3" s="24" t="s"/>
+    </row>
+    <row r="4" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A4" s="17" t="s"/>
+      <c r="B4" s="25">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="25">
         <v>18</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="25">
         <v>5</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="25">
         <v>1</v>
       </c>
       <c r="H4" s="17">
         <v>0</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="10">
-        <v>1</v>
-      </c>
-      <c r="K4" s="7">
+      <c r="I4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="25">
         <v>1000</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="24">
+        <v>3</v>
       </c>
       <c r="Z4" s="5">
         <v>1</v>
       </c>
-      <c r="AA4" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A5" s="14" t="s"/>
-      <c r="B5" s="7">
+      <c r="AA4" s="11" t="s"/>
+      <c r="AB4" s="24" t="s"/>
+    </row>
+    <row r="5" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A5" s="17" t="s"/>
+      <c r="B5" s="25">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>15</v>
-      </c>
-      <c r="F5" s="7">
-        <v>10</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="C5" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="25">
         <v>2</v>
+      </c>
+      <c r="E5" s="25">
+        <v>32</v>
+      </c>
+      <c r="F5" s="25">
+        <v>24</v>
+      </c>
+      <c r="G5" s="25">
+        <v>14</v>
       </c>
       <c r="H5" s="17">
         <v>0</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="10">
-        <v>1</v>
-      </c>
-      <c r="K5" s="7">
-        <v>800</v>
+      <c r="I5" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="25">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="24">
+        <v>3</v>
       </c>
       <c r="Z5" s="5">
         <v>2</v>
       </c>
-      <c r="AA5" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A6" s="14" t="s"/>
-      <c r="B6" s="7">
+      <c r="AA5" s="11" t="s"/>
+      <c r="AB5" s="24" t="s"/>
+    </row>
+    <row r="6" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A6" s="17" t="s"/>
+      <c r="B6" s="25">
         <v>3</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>25</v>
-      </c>
-      <c r="F6" s="7">
-        <v>15</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="25">
         <v>3</v>
+      </c>
+      <c r="E6" s="25">
+        <v>48</v>
+      </c>
+      <c r="F6" s="25">
+        <v>38</v>
+      </c>
+      <c r="G6" s="25">
+        <v>10</v>
       </c>
       <c r="H6" s="17">
         <v>0</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="10">
-        <v>2</v>
-      </c>
-      <c r="K6" s="7">
-        <v>600</v>
+      <c r="I6" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="25">
+        <v>800</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="M6" s="24">
+        <v>3</v>
       </c>
       <c r="Z6" s="5">
         <v>3</v>
       </c>
-      <c r="AA6" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A7" s="14" t="s"/>
-      <c r="B7" s="7">
+      <c r="AA6" s="11" t="s"/>
+      <c r="AB6" s="24" t="s"/>
+    </row>
+    <row r="7" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A7" s="17" t="s"/>
+      <c r="B7" s="25">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2</v>
-      </c>
-      <c r="E7" s="7">
-        <v>32</v>
-      </c>
-      <c r="F7" s="7">
-        <v>24</v>
-      </c>
-      <c r="G7" s="7">
-        <v>14</v>
+      <c r="C7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="25">
+        <v>4</v>
+      </c>
+      <c r="E7" s="25">
+        <v>72</v>
+      </c>
+      <c r="F7" s="25">
+        <v>62</v>
+      </c>
+      <c r="G7" s="25">
+        <v>8</v>
       </c>
       <c r="H7" s="17">
         <v>0</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="10">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7">
-        <v>1000</v>
+      <c r="I7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="25">
+        <v>600</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="M7" s="24">
+        <v>3</v>
       </c>
       <c r="Z7" s="5">
         <v>4</v>
       </c>
-      <c r="AA7" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A8" s="14" t="s"/>
-      <c r="B8" s="7">
+      <c r="AA7" s="11" t="s"/>
+      <c r="AB7" s="24" t="s"/>
+    </row>
+    <row r="8" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A8" s="17" t="s"/>
+      <c r="B8" s="25">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
+        <v>15</v>
+      </c>
+      <c r="F8" s="25">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25">
         <v>2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>30</v>
-      </c>
-      <c r="F8" s="7">
-        <v>22</v>
-      </c>
-      <c r="G8" s="7">
-        <v>4</v>
       </c>
       <c r="H8" s="17">
         <v>0</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="10">
-        <v>5</v>
-      </c>
-      <c r="K8" s="7">
-        <v>700</v>
+      <c r="I8" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="25">
+        <v>800</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="24">
+        <v>3</v>
       </c>
       <c r="Z8" s="5">
         <v>5</v>
       </c>
-      <c r="AA8" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="39.95" customHeight="1">
-      <c r="A9" s="14" t="s"/>
-      <c r="B9" s="7">
+      <c r="AA8" s="11" t="s"/>
+      <c r="AB8" s="24" t="s"/>
+    </row>
+    <row r="9" spans="1:28" ht="39.95" customHeight="1">
+      <c r="A9" s="17" t="s"/>
+      <c r="B9" s="25">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="25">
         <v>2</v>
       </c>
-      <c r="E9" s="7">
-        <v>38</v>
-      </c>
-      <c r="F9" s="7">
-        <v>25</v>
-      </c>
-      <c r="G9" s="7">
-        <v>3</v>
+      <c r="E9" s="25">
+        <v>30</v>
+      </c>
+      <c r="F9" s="25">
+        <v>22</v>
+      </c>
+      <c r="G9" s="25">
+        <v>4</v>
       </c>
       <c r="H9" s="17">
         <v>0</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="I9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="25">
+        <v>700</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="M9" s="24">
         <v>3</v>
       </c>
-      <c r="K9" s="7">
-        <v>400</v>
-      </c>
       <c r="Z9" s="5" t="s"/>
-      <c r="AA9" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A10" s="14" t="s"/>
-      <c r="B10" s="7">
+      <c r="AA9" s="11" t="s"/>
+      <c r="AB9" s="24" t="s"/>
+    </row>
+    <row r="10" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A10" s="17" t="s"/>
+      <c r="B10" s="25">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="25">
         <v>3</v>
       </c>
-      <c r="E10" s="7">
-        <v>48</v>
-      </c>
-      <c r="F10" s="7">
-        <v>38</v>
-      </c>
-      <c r="G10" s="7">
-        <v>10</v>
+      <c r="E10" s="25">
+        <v>50</v>
+      </c>
+      <c r="F10" s="25">
+        <v>36</v>
+      </c>
+      <c r="G10" s="25">
+        <v>14</v>
       </c>
       <c r="H10" s="17">
         <v>0</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A11" s="14" t="s"/>
-      <c r="B11" s="7">
+      <c r="I10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K10" s="25">
+        <v>600</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A11" s="17" t="s"/>
+      <c r="B11" s="25">
         <v>8</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="7">
-        <v>3</v>
-      </c>
-      <c r="E11" s="7">
-        <v>50</v>
-      </c>
-      <c r="F11" s="7">
-        <v>36</v>
-      </c>
-      <c r="G11" s="7">
-        <v>14</v>
+      <c r="C11" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="25">
+        <v>5</v>
+      </c>
+      <c r="E11" s="25">
+        <v>80</v>
+      </c>
+      <c r="F11" s="25">
+        <v>70</v>
+      </c>
+      <c r="G11" s="25">
+        <v>30</v>
       </c>
       <c r="H11" s="17">
         <v>0</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="10">
-        <v>4</v>
-      </c>
-      <c r="K11" s="7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A12" s="14" t="s"/>
-      <c r="B12" s="7">
+      <c r="I11" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="K11" s="25">
+        <v>800</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="M11" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A12" s="17" t="s"/>
+      <c r="B12" s="25">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="7">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7">
-        <v>65</v>
-      </c>
-      <c r="F12" s="7">
-        <v>52</v>
-      </c>
-      <c r="G12" s="7">
-        <v>6</v>
+      <c r="C12" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1</v>
+      </c>
+      <c r="E12" s="25">
+        <v>18</v>
+      </c>
+      <c r="F12" s="25">
+        <v>5</v>
+      </c>
+      <c r="G12" s="25">
+        <v>1</v>
       </c>
       <c r="H12" s="17">
         <v>0</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="10">
+      <c r="I12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="K12" s="25">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="24">
         <v>3</v>
       </c>
-      <c r="K12" s="7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A13" s="14" t="s"/>
-      <c r="B13" s="7">
+    </row>
+    <row r="13" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A13" s="17" t="s"/>
+      <c r="B13" s="25">
         <v>10</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7">
-        <v>72</v>
-      </c>
-      <c r="F13" s="7">
-        <v>62</v>
-      </c>
-      <c r="G13" s="7">
-        <v>8</v>
+      <c r="C13" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="25">
+        <v>2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>32</v>
+      </c>
+      <c r="F13" s="25">
+        <v>24</v>
+      </c>
+      <c r="G13" s="25">
+        <v>14</v>
       </c>
       <c r="H13" s="17">
         <v>0</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="10">
-        <v>4</v>
-      </c>
-      <c r="K13" s="7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A14" s="14" t="s"/>
-      <c r="B14" s="7">
+      <c r="I13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="25">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="M13" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A14" s="17" t="s"/>
+      <c r="B14" s="25">
         <v>11</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4</v>
-      </c>
-      <c r="E14" s="7">
-        <v>68</v>
-      </c>
-      <c r="F14" s="7">
-        <v>58</v>
-      </c>
-      <c r="G14" s="7">
-        <v>20</v>
+      <c r="C14" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="25">
+        <v>3</v>
+      </c>
+      <c r="E14" s="25">
+        <v>48</v>
+      </c>
+      <c r="F14" s="25">
+        <v>38</v>
+      </c>
+      <c r="G14" s="25">
+        <v>10</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="10">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A15" s="14" t="s"/>
-      <c r="B15" s="7">
+      <c r="I14" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="25">
+        <v>800</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A15" s="17" t="s"/>
+      <c r="B15" s="25">
         <v>12</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="25">
         <v>4</v>
       </c>
-      <c r="E15" s="7">
-        <v>78</v>
-      </c>
-      <c r="F15" s="7">
-        <v>68</v>
-      </c>
-      <c r="G15" s="7">
-        <v>12</v>
+      <c r="E15" s="25">
+        <v>72</v>
+      </c>
+      <c r="F15" s="25">
+        <v>62</v>
+      </c>
+      <c r="G15" s="25">
+        <v>8</v>
       </c>
       <c r="H15" s="17">
         <v>0</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="K15" s="25">
+        <v>600</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A16" s="17" t="s"/>
+      <c r="B16" s="25">
+        <v>13</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="25">
+        <v>3</v>
+      </c>
+      <c r="E16" s="25">
         <v>48</v>
       </c>
-      <c r="J15" s="10">
-        <v>3</v>
-      </c>
-      <c r="K15" s="7">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A16" s="14" t="s"/>
-      <c r="B16" s="7">
-        <v>13</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5</v>
-      </c>
-      <c r="E16" s="7">
-        <v>80</v>
-      </c>
-      <c r="F16" s="7">
-        <v>70</v>
-      </c>
-      <c r="G16" s="7">
-        <v>30</v>
+      <c r="F16" s="25">
+        <v>38</v>
+      </c>
+      <c r="G16" s="25">
+        <v>10</v>
       </c>
       <c r="H16" s="17">
         <v>0</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="10">
-        <v>6</v>
-      </c>
-      <c r="K16" s="7">
+      <c r="I16" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="K16" s="25">
         <v>800</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A17" s="14" t="s"/>
-      <c r="B17" s="7">
+      <c r="L16" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="M16" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A17" s="17" t="s"/>
+      <c r="B17" s="25">
         <v>14</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="7">
-        <v>5</v>
-      </c>
-      <c r="E17" s="7">
-        <v>90</v>
-      </c>
-      <c r="F17" s="7">
-        <v>82</v>
-      </c>
-      <c r="G17" s="7">
-        <v>48</v>
+      <c r="C17" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="25">
+        <v>4</v>
+      </c>
+      <c r="E17" s="25">
+        <v>72</v>
+      </c>
+      <c r="F17" s="25">
+        <v>62</v>
+      </c>
+      <c r="G17" s="25">
+        <v>8</v>
       </c>
       <c r="H17" s="17">
         <v>0</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="10">
+      <c r="I17" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" s="25">
+        <v>600</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="M17" s="24">
         <v>1</v>
       </c>
-      <c r="K17" s="7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="39.95" customHeight="1">
-      <c r="A18" s="14" t="s"/>
-      <c r="B18" s="7">
+    </row>
+    <row r="18" spans="1:13" ht="39.95" customHeight="1">
+      <c r="A18" s="17" t="s"/>
+      <c r="B18" s="25">
         <v>15</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="25">
         <v>5</v>
       </c>
-      <c r="E18" s="7">
-        <v>100</v>
-      </c>
-      <c r="F18" s="7">
-        <v>95</v>
-      </c>
-      <c r="G18" s="7">
-        <v>100</v>
+      <c r="E18" s="25">
+        <v>80</v>
+      </c>
+      <c r="F18" s="25">
+        <v>70</v>
+      </c>
+      <c r="G18" s="25">
+        <v>30</v>
       </c>
       <c r="H18" s="17">
         <v>0</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="10">
-        <v>6</v>
-      </c>
-      <c r="K18" s="7">
+      <c r="I18" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="25">
+        <v>800</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="M18" s="24">
         <v>1</v>
       </c>
     </row>
@@ -3699,51 +4004,6 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B4">
-      <formula1>AND(ISNUMBER(B4),B4=INT(B4),B4&gt;0,COUNTIFS($B$4:$B$203,B4)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B5">
-      <formula1>AND(ISNUMBER(B5),B5=INT(B5),B5&gt;0,COUNTIFS($B$4:$B$203,B5)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B6">
-      <formula1>AND(ISNUMBER(B6),B6=INT(B6),B6&gt;0,COUNTIFS($B$4:$B$203,B6)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B7">
-      <formula1>AND(ISNUMBER(B7),B7=INT(B7),B7&gt;0,COUNTIFS($B$4:$B$203,B7)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B8">
-      <formula1>AND(ISNUMBER(B8),B8=INT(B8),B8&gt;0,COUNTIFS($B$4:$B$203,B8)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B9">
-      <formula1>AND(ISNUMBER(B9),B9=INT(B9),B9&gt;0,COUNTIFS($B$4:$B$203,B9)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B10">
-      <formula1>AND(ISNUMBER(B10),B10=INT(B10),B10&gt;0,COUNTIFS($B$4:$B$203,B10)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B11">
-      <formula1>AND(ISNUMBER(B11),B11=INT(B11),B11&gt;0,COUNTIFS($B$4:$B$203,B11)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B12">
-      <formula1>AND(ISNUMBER(B12),B12=INT(B12),B12&gt;0,COUNTIFS($B$4:$B$203,B12)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B13">
-      <formula1>AND(ISNUMBER(B13),B13=INT(B13),B13&gt;0,COUNTIFS($B$4:$B$203,B13)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B14">
-      <formula1>AND(ISNUMBER(B14),B14=INT(B14),B14&gt;0,COUNTIFS($B$4:$B$203,B14)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B15">
-      <formula1>AND(ISNUMBER(B15),B15=INT(B15),B15&gt;0,COUNTIFS($B$4:$B$203,B15)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B16">
-      <formula1>AND(ISNUMBER(B16),B16=INT(B16),B16&gt;0,COUNTIFS($B$4:$B$203,B16)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B17">
-      <formula1>AND(ISNUMBER(B17),B17=INT(B17),B17&gt;0,COUNTIFS($B$4:$B$203,B17)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B18">
-      <formula1>AND(ISNUMBER(B18),B18=INT(B18),B18&gt;0,COUNTIFS($B$4:$B$203,B18)=1)</formula1>
-    </dataValidation>
     <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B19">
       <formula1>AND(ISNUMBER(B19),B19=INT(B19),B19&gt;0,COUNTIFS($B$4:$B$203,B19)=1)</formula1>
     </dataValidation>
@@ -4293,26 +4553,18 @@
     <dataValidation type="custom" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="" sqref="B201">
       <formula1>AND(ISNUMBER(B201),B201=INT(B201),B201&gt;0,COUNTIFS($B$4:$B$203,B201)=1)</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="1" errorTitle="出现阶段无效" error="请选择1至5阶段。" sqref="D4:D201">
+    <dataValidation type="list" operator="between" allowBlank="1" errorTitle="出现阶段无效" error="请选择1至5阶段。" sqref="D19:D201">
       <formula1>$Z$4:$Z$8</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="E4:E201">
+    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="E19:E201">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="F4:F201">
+    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="F19:F201">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="G4:G201">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="H4">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="H5:H18">
+    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="三维数值无效" error="生命、力量、智力均填写0至100的整数。" sqref="G19:G201">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4320,10 +4572,7 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="1" errorTitle="出现场地无效" error="请从场地下拉列表中选择。" sqref="J19:J201">
-      <formula1>$AA$4:$AA$9</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="抽取权重无效" error="权重填写0或正整数，默认1000；0表示不参与抽取。" sqref="K4:K201">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="抽取权重无效" error="权重填写0或正整数，默认1000；0表示不参与抽取。" sqref="K19:K201">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
